--- a/P/Project _01/outputs/regression_input_data.xlsx
+++ b/P/Project _01/outputs/regression_input_data.xlsx
@@ -11,6 +11,9 @@
     <sheet name="SummaryStats" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ModelSummary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="HypothesisTests" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ForecastTests" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ForecastSeries" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ForecastCalibration" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22979,4 +22982,5522 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Null Hypothesis</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Alternative Hypothesis</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Statistic</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Reject H0</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Better Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bias t-test</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mean forecast error = 0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mean forecast error != 0</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.874158207253127</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.434915488093747e-10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mincer-Zarnowitz joint F-test</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Intercept = 0 and slope = 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Forecast is not unbiased and efficient</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>25.69033785657524</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.355092500520935e-10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Directional accuracy binomial test</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Directional accuracy = 50%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Directional accuracy &gt; 50%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0004830665287370928</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mincer-Zarnowitz intercept t-test</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Intercept = 0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Intercept != 0</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.284882338631352</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02368503660049203</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mincer-Zarnowitz slope t-test</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Slope = 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Slope != 1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.842858952978913</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06727222247671194</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Diebold-Mariano (Squared Error)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Equal predictive accuracy vs random-walk benchmark</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Forecast accuracy differs from benchmark</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.096134710671916</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2730198264486918</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ARIMAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Diebold-Mariano (Absolute Error)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Equal predictive accuracy vs random-walk benchmark</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Forecast accuracy differs from benchmark</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.126477936966567</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2599632742104769</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Random Walk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ljung-Box Q(4)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Forecast errors are not autocorrelated</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Forecast errors are autocorrelated</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>530.4591127948179</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.727919427187857e-113</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ljung-Box Q(8)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Forecast errors are not autocorrelated</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Forecast errors are autocorrelated</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>923.2357439803013</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.488169457514574e-194</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jarque-Bera</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Forecast errors are normally distributed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Forecast errors are not normally distributed</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.738265040442363</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.05674813309187698</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J157"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ActualPrice</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ForecastPrice</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>RandomWalkBenchmark</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ForecastError</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>BenchmarkError</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>AbsForecastError</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AbsBenchmarkError</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SquaredForecastError</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SquaredBenchmarkError</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>42741</v>
+      </c>
+      <c r="B2" t="n">
+        <v>53.9900016784668</v>
+      </c>
+      <c r="C2" t="n">
+        <v>53.52651453040167</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.463487148065127</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.270000457763679</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.463487148065127</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.270000457763679</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.214820336421545</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.07290024719259619</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>42748</v>
+      </c>
+      <c r="B3" t="n">
+        <v>52.36999893188477</v>
+      </c>
+      <c r="C3" t="n">
+        <v>54.38004795437161</v>
+      </c>
+      <c r="D3" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-2.010049022486832</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.350002288818345</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.010049022486832</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.350002288818345</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.040297072800271</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.822506179814771</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>42755</v>
+      </c>
+      <c r="B4" t="n">
+        <v>52.41999816894531</v>
+      </c>
+      <c r="C4" t="n">
+        <v>54.27051986367545</v>
+      </c>
+      <c r="D4" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.850521694730141</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.300003051757805</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.850521694730141</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.300003051757805</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.424430542666911</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.690007934579607</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>42762</v>
+      </c>
+      <c r="B5" t="n">
+        <v>53.16999816894531</v>
+      </c>
+      <c r="C5" t="n">
+        <v>55.0270552357098</v>
+      </c>
+      <c r="D5" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.857057066764483</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.5500030517578054</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.857057066764483</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5500030517578054</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.448660949219906</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3025033569428991</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>42769</v>
+      </c>
+      <c r="B6" t="n">
+        <v>53.83000183105469</v>
+      </c>
+      <c r="C6" t="n">
+        <v>54.78400356977833</v>
+      </c>
+      <c r="D6" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.9540017387236475</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1100006103515696</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9540017387236475</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1100006103515696</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9101193174877426</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01210013427771784</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>42776</v>
+      </c>
+      <c r="B7" t="n">
+        <v>53.86000061035156</v>
+      </c>
+      <c r="C7" t="n">
+        <v>55.46770372325025</v>
+      </c>
+      <c r="D7" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.60770311289869</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1399993896484446</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.60770311289869</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1399993896484446</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.584709299224139</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01959982910193702</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>42783</v>
+      </c>
+      <c r="B8" t="n">
+        <v>53.40000152587891</v>
+      </c>
+      <c r="C8" t="n">
+        <v>55.39225875646948</v>
+      </c>
+      <c r="D8" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.992257230590567</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.3199996948242045</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.992257230590567</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3199996948242045</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.969088872840397</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.102399804687584</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>42790</v>
+      </c>
+      <c r="B9" t="n">
+        <v>53.9900016784668</v>
+      </c>
+      <c r="C9" t="n">
+        <v>54.75758101605417</v>
+      </c>
+      <c r="D9" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.7675793375873781</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.270000457763679</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7675793375873781</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.270000457763679</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5891780394910781</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.07290024719259619</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>42797</v>
+      </c>
+      <c r="B10" t="n">
+        <v>53.33000183105469</v>
+      </c>
+      <c r="C10" t="n">
+        <v>55.328398876834</v>
+      </c>
+      <c r="D10" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.998397045779313</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.3899993896484304</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.998397045779313</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3899993896484304</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.993590752579487</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1520995239261482</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>42804</v>
+      </c>
+      <c r="B11" t="n">
+        <v>48.4900016784668</v>
+      </c>
+      <c r="C11" t="n">
+        <v>53.70247325458025</v>
+      </c>
+      <c r="D11" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-5.212471576113451</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-5.229999542236321</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.212471576113451</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.229999542236321</v>
+      </c>
+      <c r="I11" t="n">
+        <v>27.16985993179064</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27.35289521179213</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>42811</v>
+      </c>
+      <c r="B12" t="n">
+        <v>48.77999877929688</v>
+      </c>
+      <c r="C12" t="n">
+        <v>54.70990163893141</v>
+      </c>
+      <c r="D12" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-5.929902859634531</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-4.940002441406236</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.929902859634531</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.940002441406236</v>
+      </c>
+      <c r="I12" t="n">
+        <v>35.16374792470179</v>
+      </c>
+      <c r="J12" t="n">
+        <v>24.40362412109957</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>42818</v>
+      </c>
+      <c r="B13" t="n">
+        <v>47.97000122070312</v>
+      </c>
+      <c r="C13" t="n">
+        <v>54.15713533752423</v>
+      </c>
+      <c r="D13" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-6.187134116821113</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.187134116821113</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>38.28062857953178</v>
+      </c>
+      <c r="J13" t="n">
+        <v>33.0625</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>42825</v>
+      </c>
+      <c r="B14" t="n">
+        <v>50.59999847412109</v>
+      </c>
+      <c r="C14" t="n">
+        <v>54.98593634009133</v>
+      </c>
+      <c r="D14" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-4.385937865970241</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3.120002746582031</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.385937865970241</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.120002746582031</v>
+      </c>
+      <c r="I14" t="n">
+        <v>19.2364509641516</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9.734417138679419</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>42832</v>
+      </c>
+      <c r="B15" t="n">
+        <v>52.2400016784668</v>
+      </c>
+      <c r="C15" t="n">
+        <v>54.95799797955164</v>
+      </c>
+      <c r="D15" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.717996301084838</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.479999542236321</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.717996301084838</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.479999542236321</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.387503892710862</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.19039864501972</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>42839</v>
+      </c>
+      <c r="B16" t="n">
+        <v>53.18000030517578</v>
+      </c>
+      <c r="C16" t="n">
+        <v>54.53474091790837</v>
+      </c>
+      <c r="D16" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.354740612732584</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.5400009155273366</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.354740612732584</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5400009155273366</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.835322127787058</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.2916009887703618</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>42846</v>
+      </c>
+      <c r="B17" t="n">
+        <v>49.61999893188477</v>
+      </c>
+      <c r="C17" t="n">
+        <v>53.74964868140943</v>
+      </c>
+      <c r="D17" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-4.12964974952466</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-4.100002288818345</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.12964974952466</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.100002288818345</v>
+      </c>
+      <c r="I17" t="n">
+        <v>17.05400705374909</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16.81001876831567</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>42853</v>
+      </c>
+      <c r="B18" t="n">
+        <v>49.33000183105469</v>
+      </c>
+      <c r="C18" t="n">
+        <v>54.50029541142933</v>
+      </c>
+      <c r="D18" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-5.17029358037464</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-4.38999938964843</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.17029358037464</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.38999938964843</v>
+      </c>
+      <c r="I18" t="n">
+        <v>26.73193570726321</v>
+      </c>
+      <c r="J18" t="n">
+        <v>19.27209464111359</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>42860</v>
+      </c>
+      <c r="B19" t="n">
+        <v>46.22000122070312</v>
+      </c>
+      <c r="C19" t="n">
+        <v>53.42486309586831</v>
+      </c>
+      <c r="D19" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-7.204861875165193</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.204861875165193</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>51.9100346402089</v>
+      </c>
+      <c r="J19" t="n">
+        <v>56.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>42867</v>
+      </c>
+      <c r="B20" t="n">
+        <v>47.84000015258789</v>
+      </c>
+      <c r="C20" t="n">
+        <v>53.16590085626851</v>
+      </c>
+      <c r="D20" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-5.325900703680617</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-5.880001068115227</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.325900703680617</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.880001068115227</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28.36521830546569</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.57441256103621</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>42874</v>
+      </c>
+      <c r="B21" t="n">
+        <v>50.33000183105469</v>
+      </c>
+      <c r="C21" t="n">
+        <v>54.18113651752684</v>
+      </c>
+      <c r="D21" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-3.851134686472157</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-3.38999938964843</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.851134686472157</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.38999938964843</v>
+      </c>
+      <c r="I21" t="n">
+        <v>14.831238373349</v>
+      </c>
+      <c r="J21" t="n">
+        <v>11.49209586181673</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>42881</v>
+      </c>
+      <c r="B22" t="n">
+        <v>49.79999923706055</v>
+      </c>
+      <c r="C22" t="n">
+        <v>54.62785056169044</v>
+      </c>
+      <c r="D22" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-4.827851324629897</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.920001983642571</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.827851324629897</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.920001983642571</v>
+      </c>
+      <c r="I22" t="n">
+        <v>23.30814841273065</v>
+      </c>
+      <c r="J22" t="n">
+        <v>15.36641555176169</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>42888</v>
+      </c>
+      <c r="B23" t="n">
+        <v>47.65999984741211</v>
+      </c>
+      <c r="C23" t="n">
+        <v>53.70244941405937</v>
+      </c>
+      <c r="D23" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-6.042449566647257</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-6.060001373291009</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.042449566647257</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.060001373291009</v>
+      </c>
+      <c r="I23" t="n">
+        <v>36.51119676547562</v>
+      </c>
+      <c r="J23" t="n">
+        <v>36.72361664428891</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>42895</v>
+      </c>
+      <c r="B24" t="n">
+        <v>45.83000183105469</v>
+      </c>
+      <c r="C24" t="n">
+        <v>53.76058614968359</v>
+      </c>
+      <c r="D24" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-7.930584318628902</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-7.88999938964843</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7.930584318628902</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.88999938964843</v>
+      </c>
+      <c r="I24" t="n">
+        <v>62.89416763488266</v>
+      </c>
+      <c r="J24" t="n">
+        <v>62.2520903686526</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>42902</v>
+      </c>
+      <c r="B25" t="n">
+        <v>44.7400016784668</v>
+      </c>
+      <c r="C25" t="n">
+        <v>53.86682302436336</v>
+      </c>
+      <c r="D25" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-9.126821345896559</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-8.979999542236321</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.126821345896559</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8.979999542236321</v>
+      </c>
+      <c r="I25" t="n">
+        <v>83.29886787991308</v>
+      </c>
+      <c r="J25" t="n">
+        <v>80.64039177856453</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>42909</v>
+      </c>
+      <c r="B26" t="n">
+        <v>43.0099983215332</v>
+      </c>
+      <c r="C26" t="n">
+        <v>53.29118070043565</v>
+      </c>
+      <c r="D26" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-10.28118237890245</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-10.71000289916991</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10.28118237890245</v>
+      </c>
+      <c r="H26" t="n">
+        <v>10.71000289916991</v>
+      </c>
+      <c r="I26" t="n">
+        <v>105.7027111082542</v>
+      </c>
+      <c r="J26" t="n">
+        <v>114.704162100228</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>42916</v>
+      </c>
+      <c r="B27" t="n">
+        <v>46.04000091552734</v>
+      </c>
+      <c r="C27" t="n">
+        <v>54.78734054280183</v>
+      </c>
+      <c r="D27" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-8.747339627274492</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-7.680000305175781</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8.747339627274492</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7.680000305175781</v>
+      </c>
+      <c r="I27" t="n">
+        <v>76.51595055488664</v>
+      </c>
+      <c r="J27" t="n">
+        <v>58.98240468750009</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>42923</v>
+      </c>
+      <c r="B28" t="n">
+        <v>44.22999954223633</v>
+      </c>
+      <c r="C28" t="n">
+        <v>53.7532315690064</v>
+      </c>
+      <c r="D28" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-9.523232026770074</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-9.49000167846679</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9.523232026770074</v>
+      </c>
+      <c r="H28" t="n">
+        <v>9.49000167846679</v>
+      </c>
+      <c r="I28" t="n">
+        <v>90.69194823569926</v>
+      </c>
+      <c r="J28" t="n">
+        <v>90.06013185730249</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>42930</v>
+      </c>
+      <c r="B29" t="n">
+        <v>46.54000091552734</v>
+      </c>
+      <c r="C29" t="n">
+        <v>54.40861323012767</v>
+      </c>
+      <c r="D29" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-7.868612314600334</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-7.180000305175781</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.868612314600334</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7.180000305175781</v>
+      </c>
+      <c r="I29" t="n">
+        <v>61.91505975748002</v>
+      </c>
+      <c r="J29" t="n">
+        <v>51.55240438232431</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>42937</v>
+      </c>
+      <c r="B30" t="n">
+        <v>45.77000045776367</v>
+      </c>
+      <c r="C30" t="n">
+        <v>55.20751308561493</v>
+      </c>
+      <c r="D30" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-9.437512627851262</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-7.950000762939446</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.437512627851262</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7.950000762939446</v>
+      </c>
+      <c r="I30" t="n">
+        <v>89.06664460085204</v>
+      </c>
+      <c r="J30" t="n">
+        <v>63.20251213073777</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>42944</v>
+      </c>
+      <c r="B31" t="n">
+        <v>49.70999908447266</v>
+      </c>
+      <c r="C31" t="n">
+        <v>55.55979066622854</v>
+      </c>
+      <c r="D31" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-5.849791581755873</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-4.010002136230455</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.849791581755873</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.010002136230455</v>
+      </c>
+      <c r="I31" t="n">
+        <v>34.22006154998189</v>
+      </c>
+      <c r="J31" t="n">
+        <v>16.08011713257281</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>42951</v>
+      </c>
+      <c r="B32" t="n">
+        <v>49.58000183105469</v>
+      </c>
+      <c r="C32" t="n">
+        <v>55.76021155135346</v>
+      </c>
+      <c r="D32" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-6.18020972029877</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-4.13999938964843</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.18020972029877</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.13999938964843</v>
+      </c>
+      <c r="I32" t="n">
+        <v>38.1949921868754</v>
+      </c>
+      <c r="J32" t="n">
+        <v>17.13959494628937</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>42958</v>
+      </c>
+      <c r="B33" t="n">
+        <v>48.81999969482422</v>
+      </c>
+      <c r="C33" t="n">
+        <v>55.49849069141285</v>
+      </c>
+      <c r="D33" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-6.678490996588636</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-4.900001525878899</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6.678490996588636</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.900001525878899</v>
+      </c>
+      <c r="I33" t="n">
+        <v>44.60224199151547</v>
+      </c>
+      <c r="J33" t="n">
+        <v>24.01001495361554</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>42965</v>
+      </c>
+      <c r="B34" t="n">
+        <v>48.5099983215332</v>
+      </c>
+      <c r="C34" t="n">
+        <v>55.17076359606718</v>
+      </c>
+      <c r="D34" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-6.660765274533972</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-5.210002899169915</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6.660765274533972</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.210002899169915</v>
+      </c>
+      <c r="I34" t="n">
+        <v>44.36579404243762</v>
+      </c>
+      <c r="J34" t="n">
+        <v>27.14413020935892</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>42972</v>
+      </c>
+      <c r="B35" t="n">
+        <v>47.86999893188477</v>
+      </c>
+      <c r="C35" t="n">
+        <v>55.39060634445879</v>
+      </c>
+      <c r="D35" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-7.520607412574016</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-5.850002288818345</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.520607412574016</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.850002288818345</v>
+      </c>
+      <c r="I35" t="n">
+        <v>56.55953585406323</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.22252677917988</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>42979</v>
+      </c>
+      <c r="B36" t="n">
+        <v>47.29000091552734</v>
+      </c>
+      <c r="C36" t="n">
+        <v>56.05047695229753</v>
+      </c>
+      <c r="D36" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-8.760476036770193</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-6.430000305175781</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.760476036770193</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.430000305175781</v>
+      </c>
+      <c r="I36" t="n">
+        <v>76.74594039082479</v>
+      </c>
+      <c r="J36" t="n">
+        <v>41.34490392456064</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>42986</v>
+      </c>
+      <c r="B37" t="n">
+        <v>47.47999954223633</v>
+      </c>
+      <c r="C37" t="n">
+        <v>55.02032262241875</v>
+      </c>
+      <c r="D37" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-7.540323080182418</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-6.24000167846679</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7.540323080182418</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.24000167846679</v>
+      </c>
+      <c r="I37" t="n">
+        <v>56.85647215353167</v>
+      </c>
+      <c r="J37" t="n">
+        <v>38.93762094726836</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>42993</v>
+      </c>
+      <c r="B38" t="n">
+        <v>49.88999938964844</v>
+      </c>
+      <c r="C38" t="n">
+        <v>55.97925841542967</v>
+      </c>
+      <c r="D38" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-6.089259025781232</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-3.83000183105468</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6.089259025781232</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.83000183105468</v>
+      </c>
+      <c r="I38" t="n">
+        <v>37.07907548305819</v>
+      </c>
+      <c r="J38" t="n">
+        <v>14.6689140258822</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>43000</v>
+      </c>
+      <c r="B39" t="n">
+        <v>50.65999984741211</v>
+      </c>
+      <c r="C39" t="n">
+        <v>55.89671337830385</v>
+      </c>
+      <c r="D39" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-5.236713530891741</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-3.060001373291009</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5.236713530891741</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.060001373291009</v>
+      </c>
+      <c r="I39" t="n">
+        <v>27.42316860462465</v>
+      </c>
+      <c r="J39" t="n">
+        <v>9.363608404542859</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>43007</v>
+      </c>
+      <c r="B40" t="n">
+        <v>51.66999816894531</v>
+      </c>
+      <c r="C40" t="n">
+        <v>55.91587892708677</v>
+      </c>
+      <c r="D40" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-4.24588075814146</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-2.050003051757805</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4.24588075814146</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.050003051757805</v>
+      </c>
+      <c r="I40" t="n">
+        <v>18.0275034123559</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.202512512216315</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>43014</v>
+      </c>
+      <c r="B41" t="n">
+        <v>49.29000091552734</v>
+      </c>
+      <c r="C41" t="n">
+        <v>55.76450615572588</v>
+      </c>
+      <c r="D41" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-6.474505240198546</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-4.430000305175781</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.474505240198546</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.430000305175781</v>
+      </c>
+      <c r="I41" t="n">
+        <v>41.91921810535843</v>
+      </c>
+      <c r="J41" t="n">
+        <v>19.62490270385752</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>43021</v>
+      </c>
+      <c r="B42" t="n">
+        <v>51.45000076293945</v>
+      </c>
+      <c r="C42" t="n">
+        <v>56.62409851773895</v>
+      </c>
+      <c r="D42" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-5.174097754799497</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-2.270000457763665</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5.174097754799497</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.270000457763665</v>
+      </c>
+      <c r="I42" t="n">
+        <v>26.7712875762212</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5.152902078247248</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>43028</v>
+      </c>
+      <c r="B43" t="n">
+        <v>51.47000122070312</v>
+      </c>
+      <c r="C43" t="n">
+        <v>57.13703165418601</v>
+      </c>
+      <c r="D43" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-5.667030433482893</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.667030433482893</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I43" t="n">
+        <v>32.1152339340213</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5.0625</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43035</v>
+      </c>
+      <c r="B44" t="n">
+        <v>53.90000152587891</v>
+      </c>
+      <c r="C44" t="n">
+        <v>56.15605667115646</v>
+      </c>
+      <c r="D44" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-2.256055145277543</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1800003051757955</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.256055145277543</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1800003051757955</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5.089784818533275</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.0324001098633795</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43042</v>
+      </c>
+      <c r="B45" t="n">
+        <v>55.63999938964844</v>
+      </c>
+      <c r="C45" t="n">
+        <v>56.62735852496544</v>
+      </c>
+      <c r="D45" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.987359135317007</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.91999816894532</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.987359135317007</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.91999816894532</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9748780620939478</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.68639296875338</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>43049</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56.7400016784668</v>
+      </c>
+      <c r="C46" t="n">
+        <v>56.01154584013912</v>
+      </c>
+      <c r="D46" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.728455838327676</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.020000457763679</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.728455838327676</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.020000457763679</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.5306479083936773</v>
+      </c>
+      <c r="J46" t="n">
+        <v>9.12040276489283</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>43056</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56.54999923706055</v>
+      </c>
+      <c r="C47" t="n">
+        <v>56.46140857289723</v>
+      </c>
+      <c r="D47" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.08859066416331274</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.829998016357429</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.08859066416331274</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.829998016357429</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.007848305776896864</v>
+      </c>
+      <c r="J47" t="n">
+        <v>8.008888772586984</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>43063</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58.95000076293945</v>
+      </c>
+      <c r="C48" t="n">
+        <v>56.74104295002735</v>
+      </c>
+      <c r="D48" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.208957812912104</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.229999542236335</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.208957812912104</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5.229999542236335</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4.879494619225425</v>
+      </c>
+      <c r="J48" t="n">
+        <v>27.35289521179228</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58.36000061035156</v>
+      </c>
+      <c r="C49" t="n">
+        <v>57.67526325793118</v>
+      </c>
+      <c r="D49" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6847373524203846</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.639999389648445</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.6847373524203846</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.639999389648445</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.468865241799678</v>
+      </c>
+      <c r="J49" t="n">
+        <v>21.52959433593794</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>43077</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57.36000061035156</v>
+      </c>
+      <c r="C50" t="n">
+        <v>56.02659402540333</v>
+      </c>
+      <c r="D50" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.333406584948229</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.639999389648445</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.333406584948229</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3.639999389648445</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.777973120783298</v>
+      </c>
+      <c r="J50" t="n">
+        <v>13.24959555664105</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>43084</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57.29999923706055</v>
+      </c>
+      <c r="C51" t="n">
+        <v>56.93755787862795</v>
+      </c>
+      <c r="D51" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.3624413584325978</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.579998016357429</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.3624413584325978</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.579998016357429</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1313637383024669</v>
+      </c>
+      <c r="J51" t="n">
+        <v>12.81638579712313</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>43091</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="C52" t="n">
+        <v>58.38708216730187</v>
+      </c>
+      <c r="D52" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.08291905340124828</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.08291905340124828</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.006875569416959063</v>
+      </c>
+      <c r="J52" t="n">
+        <v>22.5625</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>43098</v>
+      </c>
+      <c r="B53" t="n">
+        <v>60.41999816894531</v>
+      </c>
+      <c r="C53" t="n">
+        <v>58.87983369766462</v>
+      </c>
+      <c r="D53" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.540164471280697</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.699996948242195</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.540164471280697</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6.699996948242195</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.372106598595349</v>
+      </c>
+      <c r="J53" t="n">
+        <v>44.88995910645472</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>43105</v>
+      </c>
+      <c r="B54" t="n">
+        <v>61.43999862670898</v>
+      </c>
+      <c r="C54" t="n">
+        <v>58.88493255013189</v>
+      </c>
+      <c r="D54" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.555066076577091</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7.719997406005859</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2.555066076577091</v>
+      </c>
+      <c r="H54" t="n">
+        <v>7.719997406005859</v>
+      </c>
+      <c r="I54" t="n">
+        <v>6.528362655675051</v>
+      </c>
+      <c r="J54" t="n">
+        <v>59.5983599487372</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>43112</v>
+      </c>
+      <c r="B55" t="n">
+        <v>64.30000305175781</v>
+      </c>
+      <c r="C55" t="n">
+        <v>60.00453298842955</v>
+      </c>
+      <c r="D55" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4.295470063328267</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10.58000183105469</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4.295470063328267</v>
+      </c>
+      <c r="H55" t="n">
+        <v>10.58000183105469</v>
+      </c>
+      <c r="I55" t="n">
+        <v>18.45106306494935</v>
+      </c>
+      <c r="J55" t="n">
+        <v>111.9364387451207</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>43119</v>
+      </c>
+      <c r="B56" t="n">
+        <v>63.36999893188477</v>
+      </c>
+      <c r="C56" t="n">
+        <v>61.02046038482712</v>
+      </c>
+      <c r="D56" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.349538547057648</v>
+      </c>
+      <c r="F56" t="n">
+        <v>9.649997711181655</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.349538547057648</v>
+      </c>
+      <c r="H56" t="n">
+        <v>9.649997711181655</v>
+      </c>
+      <c r="I56" t="n">
+        <v>5.520331384109763</v>
+      </c>
+      <c r="J56" t="n">
+        <v>93.12245582581117</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>43126</v>
+      </c>
+      <c r="B57" t="n">
+        <v>66.13999938964844</v>
+      </c>
+      <c r="C57" t="n">
+        <v>62.0287985450299</v>
+      </c>
+      <c r="D57" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4.111200844618537</v>
+      </c>
+      <c r="F57" t="n">
+        <v>12.41999816894532</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4.111200844618537</v>
+      </c>
+      <c r="H57" t="n">
+        <v>12.41999816894532</v>
+      </c>
+      <c r="I57" t="n">
+        <v>16.90197238479217</v>
+      </c>
+      <c r="J57" t="n">
+        <v>154.2563545166051</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>43133</v>
+      </c>
+      <c r="B58" t="n">
+        <v>65.44999694824219</v>
+      </c>
+      <c r="C58" t="n">
+        <v>60.84205796584263</v>
+      </c>
+      <c r="D58" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4.60793898239956</v>
+      </c>
+      <c r="F58" t="n">
+        <v>11.72999572753907</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4.60793898239956</v>
+      </c>
+      <c r="H58" t="n">
+        <v>11.72999572753907</v>
+      </c>
+      <c r="I58" t="n">
+        <v>21.23310166551749</v>
+      </c>
+      <c r="J58" t="n">
+        <v>137.5927997680848</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>43140</v>
+      </c>
+      <c r="B59" t="n">
+        <v>59.20000076293945</v>
+      </c>
+      <c r="C59" t="n">
+        <v>56.7411295337718</v>
+      </c>
+      <c r="D59" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.458871229167649</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5.479999542236335</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2.458871229167649</v>
+      </c>
+      <c r="H59" t="n">
+        <v>5.479999542236335</v>
+      </c>
+      <c r="I59" t="n">
+        <v>6.046047721628423</v>
+      </c>
+      <c r="J59" t="n">
+        <v>30.03039498291044</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>43147</v>
+      </c>
+      <c r="B60" t="n">
+        <v>61.68000030517578</v>
+      </c>
+      <c r="C60" t="n">
+        <v>59.14487430704099</v>
+      </c>
+      <c r="D60" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.535125998134788</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.959999084472663</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2.535125998134788</v>
+      </c>
+      <c r="H60" t="n">
+        <v>7.959999084472663</v>
+      </c>
+      <c r="I60" t="n">
+        <v>6.426863826418905</v>
+      </c>
+      <c r="J60" t="n">
+        <v>63.36158542480564</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>43154</v>
+      </c>
+      <c r="B61" t="n">
+        <v>63.54999923706055</v>
+      </c>
+      <c r="C61" t="n">
+        <v>59.88660829996149</v>
+      </c>
+      <c r="D61" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.663390937099052</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9.829998016357429</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3.663390937099052</v>
+      </c>
+      <c r="H61" t="n">
+        <v>9.829998016357429</v>
+      </c>
+      <c r="I61" t="n">
+        <v>13.42043315801947</v>
+      </c>
+      <c r="J61" t="n">
+        <v>96.62886100159099</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>43161</v>
+      </c>
+      <c r="B62" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="C62" t="n">
+        <v>58.84650547454378</v>
+      </c>
+      <c r="D62" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.403494525456225</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7.529998779296882</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2.403494525456225</v>
+      </c>
+      <c r="H62" t="n">
+        <v>7.529998779296882</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5.776785933898042</v>
+      </c>
+      <c r="J62" t="n">
+        <v>56.70088161621253</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>43168</v>
+      </c>
+      <c r="B63" t="n">
+        <v>62.04000091552734</v>
+      </c>
+      <c r="C63" t="n">
+        <v>59.24237608238669</v>
+      </c>
+      <c r="D63" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.797624833140645</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8.319999694824219</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2.797624833140645</v>
+      </c>
+      <c r="H63" t="n">
+        <v>8.319999694824219</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7.826704707005224</v>
+      </c>
+      <c r="J63" t="n">
+        <v>69.22239492187509</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>43175</v>
+      </c>
+      <c r="B64" t="n">
+        <v>62.34000015258789</v>
+      </c>
+      <c r="C64" t="n">
+        <v>59.01370732702951</v>
+      </c>
+      <c r="D64" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3.326292825558383</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8.619998931884773</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3.326292825558383</v>
+      </c>
+      <c r="H64" t="n">
+        <v>8.619998931884773</v>
+      </c>
+      <c r="I64" t="n">
+        <v>11.06422396136117</v>
+      </c>
+      <c r="J64" t="n">
+        <v>74.30438158569463</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>43182</v>
+      </c>
+      <c r="B65" t="n">
+        <v>65.87999725341797</v>
+      </c>
+      <c r="C65" t="n">
+        <v>56.86734986700833</v>
+      </c>
+      <c r="D65" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9.01264738640964</v>
+      </c>
+      <c r="F65" t="n">
+        <v>12.15999603271485</v>
+      </c>
+      <c r="G65" t="n">
+        <v>9.01264738640964</v>
+      </c>
+      <c r="H65" t="n">
+        <v>12.15999603271485</v>
+      </c>
+      <c r="I65" t="n">
+        <v>81.22781291175652</v>
+      </c>
+      <c r="J65" t="n">
+        <v>147.8655035156409</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>43189</v>
+      </c>
+      <c r="B66" t="n">
+        <v>64.94000244140625</v>
+      </c>
+      <c r="C66" t="n">
+        <v>57.52691829305864</v>
+      </c>
+      <c r="D66" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E66" t="n">
+        <v>7.413084148347615</v>
+      </c>
+      <c r="F66" t="n">
+        <v>11.22000122070313</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7.413084148347615</v>
+      </c>
+      <c r="H66" t="n">
+        <v>11.22000122070313</v>
+      </c>
+      <c r="I66" t="n">
+        <v>54.95381659048268</v>
+      </c>
+      <c r="J66" t="n">
+        <v>125.8884273925798</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>43196</v>
+      </c>
+      <c r="B67" t="n">
+        <v>62.06000137329102</v>
+      </c>
+      <c r="C67" t="n">
+        <v>57.31985105920563</v>
+      </c>
+      <c r="D67" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4.740150314085398</v>
+      </c>
+      <c r="F67" t="n">
+        <v>8.340000152587905</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4.740150314085398</v>
+      </c>
+      <c r="H67" t="n">
+        <v>8.340000152587905</v>
+      </c>
+      <c r="I67" t="n">
+        <v>22.46902500012389</v>
+      </c>
+      <c r="J67" t="n">
+        <v>69.55560254516628</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>43203</v>
+      </c>
+      <c r="B68" t="n">
+        <v>67.38999938964844</v>
+      </c>
+      <c r="C68" t="n">
+        <v>57.18814182583102</v>
+      </c>
+      <c r="D68" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E68" t="n">
+        <v>10.20185756381741</v>
+      </c>
+      <c r="F68" t="n">
+        <v>13.66999816894532</v>
+      </c>
+      <c r="G68" t="n">
+        <v>10.20185756381741</v>
+      </c>
+      <c r="H68" t="n">
+        <v>13.66999816894532</v>
+      </c>
+      <c r="I68" t="n">
+        <v>104.0778977524186</v>
+      </c>
+      <c r="J68" t="n">
+        <v>186.8688499389684</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>43210</v>
+      </c>
+      <c r="B69" t="n">
+        <v>68.37999725341797</v>
+      </c>
+      <c r="C69" t="n">
+        <v>58.00294319759946</v>
+      </c>
+      <c r="D69" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E69" t="n">
+        <v>10.37705405581851</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14.65999603271485</v>
+      </c>
+      <c r="G69" t="n">
+        <v>10.37705405581851</v>
+      </c>
+      <c r="H69" t="n">
+        <v>14.65999603271485</v>
+      </c>
+      <c r="I69" t="n">
+        <v>107.6832508773794</v>
+      </c>
+      <c r="J69" t="n">
+        <v>214.9154836792152</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>43217</v>
+      </c>
+      <c r="B70" t="n">
+        <v>68.09999847412109</v>
+      </c>
+      <c r="C70" t="n">
+        <v>57.6244224685943</v>
+      </c>
+      <c r="D70" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E70" t="n">
+        <v>10.4755760055268</v>
+      </c>
+      <c r="F70" t="n">
+        <v>14.37999725341798</v>
+      </c>
+      <c r="G70" t="n">
+        <v>10.4755760055268</v>
+      </c>
+      <c r="H70" t="n">
+        <v>14.37999725341798</v>
+      </c>
+      <c r="I70" t="n">
+        <v>109.7376926475688</v>
+      </c>
+      <c r="J70" t="n">
+        <v>206.7843210083085</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>43224</v>
+      </c>
+      <c r="B71" t="n">
+        <v>69.72000122070312</v>
+      </c>
+      <c r="C71" t="n">
+        <v>57.43428631316561</v>
+      </c>
+      <c r="D71" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E71" t="n">
+        <v>12.28571490753751</v>
+      </c>
+      <c r="F71" t="n">
+        <v>16.00000000000001</v>
+      </c>
+      <c r="G71" t="n">
+        <v>12.28571490753751</v>
+      </c>
+      <c r="H71" t="n">
+        <v>16.00000000000001</v>
+      </c>
+      <c r="I71" t="n">
+        <v>150.9387907892894</v>
+      </c>
+      <c r="J71" t="n">
+        <v>256.0000000000002</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>43231</v>
+      </c>
+      <c r="B72" t="n">
+        <v>70.69999694824219</v>
+      </c>
+      <c r="C72" t="n">
+        <v>58.03039930572054</v>
+      </c>
+      <c r="D72" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E72" t="n">
+        <v>12.66959764252165</v>
+      </c>
+      <c r="F72" t="n">
+        <v>16.97999572753907</v>
+      </c>
+      <c r="G72" t="n">
+        <v>12.66959764252165</v>
+      </c>
+      <c r="H72" t="n">
+        <v>16.97999572753907</v>
+      </c>
+      <c r="I72" t="n">
+        <v>160.5187044233902</v>
+      </c>
+      <c r="J72" t="n">
+        <v>288.320254907245</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>43238</v>
+      </c>
+      <c r="B73" t="n">
+        <v>71.27999877929688</v>
+      </c>
+      <c r="C73" t="n">
+        <v>57.56508676664453</v>
+      </c>
+      <c r="D73" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E73" t="n">
+        <v>13.71491201265235</v>
+      </c>
+      <c r="F73" t="n">
+        <v>17.55999755859376</v>
+      </c>
+      <c r="G73" t="n">
+        <v>13.71491201265235</v>
+      </c>
+      <c r="H73" t="n">
+        <v>17.55999755859376</v>
+      </c>
+      <c r="I73" t="n">
+        <v>188.0988115147957</v>
+      </c>
+      <c r="J73" t="n">
+        <v>308.3535142578187</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>43245</v>
+      </c>
+      <c r="B74" t="n">
+        <v>67.87999725341797</v>
+      </c>
+      <c r="C74" t="n">
+        <v>56.50638069250861</v>
+      </c>
+      <c r="D74" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E74" t="n">
+        <v>11.37361656090936</v>
+      </c>
+      <c r="F74" t="n">
+        <v>14.15999603271485</v>
+      </c>
+      <c r="G74" t="n">
+        <v>11.37361656090936</v>
+      </c>
+      <c r="H74" t="n">
+        <v>14.15999603271485</v>
+      </c>
+      <c r="I74" t="n">
+        <v>129.3591536745917</v>
+      </c>
+      <c r="J74" t="n">
+        <v>200.5054876465003</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>43252</v>
+      </c>
+      <c r="B75" t="n">
+        <v>65.80999755859375</v>
+      </c>
+      <c r="C75" t="n">
+        <v>55.2607603742391</v>
+      </c>
+      <c r="D75" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10.54923718435465</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.08999633789063</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10.54923718435465</v>
+      </c>
+      <c r="H75" t="n">
+        <v>12.08999633789063</v>
+      </c>
+      <c r="I75" t="n">
+        <v>111.2864051717707</v>
+      </c>
+      <c r="J75" t="n">
+        <v>146.1680114502089</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>43259</v>
+      </c>
+      <c r="B76" t="n">
+        <v>65.73999786376953</v>
+      </c>
+      <c r="C76" t="n">
+        <v>56.76331644202266</v>
+      </c>
+      <c r="D76" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E76" t="n">
+        <v>8.976681421746875</v>
+      </c>
+      <c r="F76" t="n">
+        <v>12.01999664306641</v>
+      </c>
+      <c r="G76" t="n">
+        <v>8.976681421746875</v>
+      </c>
+      <c r="H76" t="n">
+        <v>12.01999664306641</v>
+      </c>
+      <c r="I76" t="n">
+        <v>80.58080934753549</v>
+      </c>
+      <c r="J76" t="n">
+        <v>144.4803192993278</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>43266</v>
+      </c>
+      <c r="B77" t="n">
+        <v>65.05999755859375</v>
+      </c>
+      <c r="C77" t="n">
+        <v>56.7212266020239</v>
+      </c>
+      <c r="D77" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E77" t="n">
+        <v>8.338770956569853</v>
+      </c>
+      <c r="F77" t="n">
+        <v>11.33999633789063</v>
+      </c>
+      <c r="G77" t="n">
+        <v>8.338770956569853</v>
+      </c>
+      <c r="H77" t="n">
+        <v>11.33999633789063</v>
+      </c>
+      <c r="I77" t="n">
+        <v>69.5351010661329</v>
+      </c>
+      <c r="J77" t="n">
+        <v>128.595516943373</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>43273</v>
+      </c>
+      <c r="B78" t="n">
+        <v>68.58000183105469</v>
+      </c>
+      <c r="C78" t="n">
+        <v>56.65264263098136</v>
+      </c>
+      <c r="D78" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E78" t="n">
+        <v>11.92735920007333</v>
+      </c>
+      <c r="F78" t="n">
+        <v>14.86000061035157</v>
+      </c>
+      <c r="G78" t="n">
+        <v>11.92735920007333</v>
+      </c>
+      <c r="H78" t="n">
+        <v>14.86000061035157</v>
+      </c>
+      <c r="I78" t="n">
+        <v>142.2618974875738</v>
+      </c>
+      <c r="J78" t="n">
+        <v>220.819618139649</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>43280</v>
+      </c>
+      <c r="B79" t="n">
+        <v>74.15000152587891</v>
+      </c>
+      <c r="C79" t="n">
+        <v>56.10796464346157</v>
+      </c>
+      <c r="D79" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E79" t="n">
+        <v>18.04203688241734</v>
+      </c>
+      <c r="F79" t="n">
+        <v>20.43000030517579</v>
+      </c>
+      <c r="G79" t="n">
+        <v>18.04203688241734</v>
+      </c>
+      <c r="H79" t="n">
+        <v>20.43000030517579</v>
+      </c>
+      <c r="I79" t="n">
+        <v>325.5150948665074</v>
+      </c>
+      <c r="J79" t="n">
+        <v>417.3849124694828</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>43287</v>
+      </c>
+      <c r="B80" t="n">
+        <v>73.80000305175781</v>
+      </c>
+      <c r="C80" t="n">
+        <v>56.22096283010847</v>
+      </c>
+      <c r="D80" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E80" t="n">
+        <v>17.57904022164934</v>
+      </c>
+      <c r="F80" t="n">
+        <v>20.08000183105469</v>
+      </c>
+      <c r="G80" t="n">
+        <v>17.57904022164934</v>
+      </c>
+      <c r="H80" t="n">
+        <v>20.08000183105469</v>
+      </c>
+      <c r="I80" t="n">
+        <v>309.0226551143654</v>
+      </c>
+      <c r="J80" t="n">
+        <v>403.2064735351599</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>43294</v>
+      </c>
+      <c r="B81" t="n">
+        <v>71.01000213623047</v>
+      </c>
+      <c r="C81" t="n">
+        <v>55.35984148672875</v>
+      </c>
+      <c r="D81" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E81" t="n">
+        <v>15.65016064950171</v>
+      </c>
+      <c r="F81" t="n">
+        <v>17.29000091552735</v>
+      </c>
+      <c r="G81" t="n">
+        <v>15.65016064950171</v>
+      </c>
+      <c r="H81" t="n">
+        <v>17.29000091552735</v>
+      </c>
+      <c r="I81" t="n">
+        <v>244.9275283552119</v>
+      </c>
+      <c r="J81" t="n">
+        <v>298.9441316589366</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>43301</v>
+      </c>
+      <c r="B82" t="n">
+        <v>70.45999908447266</v>
+      </c>
+      <c r="C82" t="n">
+        <v>55.94253336506557</v>
+      </c>
+      <c r="D82" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E82" t="n">
+        <v>14.51746571940708</v>
+      </c>
+      <c r="F82" t="n">
+        <v>16.73999786376954</v>
+      </c>
+      <c r="G82" t="n">
+        <v>14.51746571940708</v>
+      </c>
+      <c r="H82" t="n">
+        <v>16.73999786376954</v>
+      </c>
+      <c r="I82" t="n">
+        <v>210.7568109141599</v>
+      </c>
+      <c r="J82" t="n">
+        <v>280.2275284790087</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>43308</v>
+      </c>
+      <c r="B83" t="n">
+        <v>68.69000244140625</v>
+      </c>
+      <c r="C83" t="n">
+        <v>55.89109092299311</v>
+      </c>
+      <c r="D83" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E83" t="n">
+        <v>12.79891151841314</v>
+      </c>
+      <c r="F83" t="n">
+        <v>14.97000122070313</v>
+      </c>
+      <c r="G83" t="n">
+        <v>12.79891151841314</v>
+      </c>
+      <c r="H83" t="n">
+        <v>14.97000122070313</v>
+      </c>
+      <c r="I83" t="n">
+        <v>163.8121360561686</v>
+      </c>
+      <c r="J83" t="n">
+        <v>224.1009365478533</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>43315</v>
+      </c>
+      <c r="B84" t="n">
+        <v>68.48999786376953</v>
+      </c>
+      <c r="C84" t="n">
+        <v>55.7623959502809</v>
+      </c>
+      <c r="D84" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E84" t="n">
+        <v>12.72760191348863</v>
+      </c>
+      <c r="F84" t="n">
+        <v>14.76999664306641</v>
+      </c>
+      <c r="G84" t="n">
+        <v>12.72760191348863</v>
+      </c>
+      <c r="H84" t="n">
+        <v>14.76999664306641</v>
+      </c>
+      <c r="I84" t="n">
+        <v>161.9918504682394</v>
+      </c>
+      <c r="J84" t="n">
+        <v>218.1528008361931</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>43322</v>
+      </c>
+      <c r="B85" t="n">
+        <v>67.62999725341797</v>
+      </c>
+      <c r="C85" t="n">
+        <v>55.20892771856432</v>
+      </c>
+      <c r="D85" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E85" t="n">
+        <v>12.42106953485365</v>
+      </c>
+      <c r="F85" t="n">
+        <v>13.90999603271485</v>
+      </c>
+      <c r="G85" t="n">
+        <v>12.42106953485365</v>
+      </c>
+      <c r="H85" t="n">
+        <v>13.90999603271485</v>
+      </c>
+      <c r="I85" t="n">
+        <v>154.2829683896695</v>
+      </c>
+      <c r="J85" t="n">
+        <v>193.4879896301429</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>43329</v>
+      </c>
+      <c r="B86" t="n">
+        <v>65.91000366210938</v>
+      </c>
+      <c r="C86" t="n">
+        <v>54.36644378996436</v>
+      </c>
+      <c r="D86" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E86" t="n">
+        <v>11.54355987214501</v>
+      </c>
+      <c r="F86" t="n">
+        <v>12.19000244140626</v>
+      </c>
+      <c r="G86" t="n">
+        <v>11.54355987214501</v>
+      </c>
+      <c r="H86" t="n">
+        <v>12.19000244140626</v>
+      </c>
+      <c r="I86" t="n">
+        <v>133.2537745217965</v>
+      </c>
+      <c r="J86" t="n">
+        <v>148.5961595214905</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>43336</v>
+      </c>
+      <c r="B87" t="n">
+        <v>68.72000122070312</v>
+      </c>
+      <c r="C87" t="n">
+        <v>55.06428098226402</v>
+      </c>
+      <c r="D87" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E87" t="n">
+        <v>13.6557202384391</v>
+      </c>
+      <c r="F87" t="n">
+        <v>15.00000000000001</v>
+      </c>
+      <c r="G87" t="n">
+        <v>13.6557202384391</v>
+      </c>
+      <c r="H87" t="n">
+        <v>15.00000000000001</v>
+      </c>
+      <c r="I87" t="n">
+        <v>186.4786952305153</v>
+      </c>
+      <c r="J87" t="n">
+        <v>225.0000000000002</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>43343</v>
+      </c>
+      <c r="B88" t="n">
+        <v>69.80000305175781</v>
+      </c>
+      <c r="C88" t="n">
+        <v>54.71793211772711</v>
+      </c>
+      <c r="D88" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E88" t="n">
+        <v>15.0820709340307</v>
+      </c>
+      <c r="F88" t="n">
+        <v>16.08000183105469</v>
+      </c>
+      <c r="G88" t="n">
+        <v>15.0820709340307</v>
+      </c>
+      <c r="H88" t="n">
+        <v>16.08000183105469</v>
+      </c>
+      <c r="I88" t="n">
+        <v>227.4688636591338</v>
+      </c>
+      <c r="J88" t="n">
+        <v>258.5664588867223</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>43350</v>
+      </c>
+      <c r="B89" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="C89" t="n">
+        <v>53.6315860213226</v>
+      </c>
+      <c r="D89" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E89" t="n">
+        <v>14.1184139786774</v>
+      </c>
+      <c r="F89" t="n">
+        <v>14.02999877929688</v>
+      </c>
+      <c r="G89" t="n">
+        <v>14.1184139786774</v>
+      </c>
+      <c r="H89" t="n">
+        <v>14.02999877929688</v>
+      </c>
+      <c r="I89" t="n">
+        <v>199.3296132733135</v>
+      </c>
+      <c r="J89" t="n">
+        <v>196.840865747072</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>43357</v>
+      </c>
+      <c r="B90" t="n">
+        <v>68.98999786376953</v>
+      </c>
+      <c r="C90" t="n">
+        <v>53.85762864696449</v>
+      </c>
+      <c r="D90" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E90" t="n">
+        <v>15.13236921680505</v>
+      </c>
+      <c r="F90" t="n">
+        <v>15.26999664306641</v>
+      </c>
+      <c r="G90" t="n">
+        <v>15.13236921680505</v>
+      </c>
+      <c r="H90" t="n">
+        <v>15.26999664306641</v>
+      </c>
+      <c r="I90" t="n">
+        <v>228.9885981137089</v>
+      </c>
+      <c r="J90" t="n">
+        <v>233.1727974792595</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>43364</v>
+      </c>
+      <c r="B91" t="n">
+        <v>70.77999877929688</v>
+      </c>
+      <c r="C91" t="n">
+        <v>55.90303274188825</v>
+      </c>
+      <c r="D91" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E91" t="n">
+        <v>14.87696603740863</v>
+      </c>
+      <c r="F91" t="n">
+        <v>17.05999755859376</v>
+      </c>
+      <c r="G91" t="n">
+        <v>14.87696603740863</v>
+      </c>
+      <c r="H91" t="n">
+        <v>17.05999755859376</v>
+      </c>
+      <c r="I91" t="n">
+        <v>221.3241184782098</v>
+      </c>
+      <c r="J91" t="n">
+        <v>291.0435166992249</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>43371</v>
+      </c>
+      <c r="B92" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="C92" t="n">
+        <v>54.97967622341679</v>
+      </c>
+      <c r="D92" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E92" t="n">
+        <v>18.27032377658321</v>
+      </c>
+      <c r="F92" t="n">
+        <v>19.52999877929688</v>
+      </c>
+      <c r="G92" t="n">
+        <v>18.27032377658321</v>
+      </c>
+      <c r="H92" t="n">
+        <v>19.52999877929688</v>
+      </c>
+      <c r="I92" t="n">
+        <v>333.8047309011818</v>
+      </c>
+      <c r="J92" t="n">
+        <v>381.4208523193377</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>43378</v>
+      </c>
+      <c r="B93" t="n">
+        <v>74.33999633789062</v>
+      </c>
+      <c r="C93" t="n">
+        <v>54.91034205931871</v>
+      </c>
+      <c r="D93" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E93" t="n">
+        <v>19.42965427857192</v>
+      </c>
+      <c r="F93" t="n">
+        <v>20.61999511718751</v>
+      </c>
+      <c r="G93" t="n">
+        <v>19.42965427857192</v>
+      </c>
+      <c r="H93" t="n">
+        <v>20.61999511718751</v>
+      </c>
+      <c r="I93" t="n">
+        <v>377.511465384828</v>
+      </c>
+      <c r="J93" t="n">
+        <v>425.1841986328366</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>43385</v>
+      </c>
+      <c r="B94" t="n">
+        <v>71.33999633789062</v>
+      </c>
+      <c r="C94" t="n">
+        <v>54.62682390510642</v>
+      </c>
+      <c r="D94" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E94" t="n">
+        <v>16.71317243278421</v>
+      </c>
+      <c r="F94" t="n">
+        <v>17.61999511718751</v>
+      </c>
+      <c r="G94" t="n">
+        <v>16.71317243278421</v>
+      </c>
+      <c r="H94" t="n">
+        <v>17.61999511718751</v>
+      </c>
+      <c r="I94" t="n">
+        <v>279.3301327679779</v>
+      </c>
+      <c r="J94" t="n">
+        <v>310.4642279297116</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>43392</v>
+      </c>
+      <c r="B95" t="n">
+        <v>69.12000274658203</v>
+      </c>
+      <c r="C95" t="n">
+        <v>54.2550362352878</v>
+      </c>
+      <c r="D95" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E95" t="n">
+        <v>14.86496651129423</v>
+      </c>
+      <c r="F95" t="n">
+        <v>15.40000152587891</v>
+      </c>
+      <c r="G95" t="n">
+        <v>14.86496651129423</v>
+      </c>
+      <c r="H95" t="n">
+        <v>15.40000152587891</v>
+      </c>
+      <c r="I95" t="n">
+        <v>220.9672293818989</v>
+      </c>
+      <c r="J95" t="n">
+        <v>237.1600469970729</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>43399</v>
+      </c>
+      <c r="B96" t="n">
+        <v>67.58999633789062</v>
+      </c>
+      <c r="C96" t="n">
+        <v>52.92612767887419</v>
+      </c>
+      <c r="D96" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E96" t="n">
+        <v>14.66386865901644</v>
+      </c>
+      <c r="F96" t="n">
+        <v>13.86999511718751</v>
+      </c>
+      <c r="G96" t="n">
+        <v>14.66386865901644</v>
+      </c>
+      <c r="H96" t="n">
+        <v>13.86999511718751</v>
+      </c>
+      <c r="I96" t="n">
+        <v>215.0290440488845</v>
+      </c>
+      <c r="J96" t="n">
+        <v>192.3767645508053</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>43406</v>
+      </c>
+      <c r="B97" t="n">
+        <v>63.13999938964844</v>
+      </c>
+      <c r="C97" t="n">
+        <v>53.60139211994006</v>
+      </c>
+      <c r="D97" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E97" t="n">
+        <v>9.538607269708379</v>
+      </c>
+      <c r="F97" t="n">
+        <v>9.41999816894532</v>
+      </c>
+      <c r="G97" t="n">
+        <v>9.538607269708379</v>
+      </c>
+      <c r="H97" t="n">
+        <v>9.41999816894532</v>
+      </c>
+      <c r="I97" t="n">
+        <v>90.98502864573354</v>
+      </c>
+      <c r="J97" t="n">
+        <v>88.73636550293317</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>43413</v>
+      </c>
+      <c r="B98" t="n">
+        <v>60.18999862670898</v>
+      </c>
+      <c r="C98" t="n">
+        <v>52.99816613442132</v>
+      </c>
+      <c r="D98" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E98" t="n">
+        <v>7.191832492287659</v>
+      </c>
+      <c r="F98" t="n">
+        <v>6.469997406005859</v>
+      </c>
+      <c r="G98" t="n">
+        <v>7.191832492287659</v>
+      </c>
+      <c r="H98" t="n">
+        <v>6.469997406005859</v>
+      </c>
+      <c r="I98" t="n">
+        <v>51.72245459712452</v>
+      </c>
+      <c r="J98" t="n">
+        <v>41.86086643372255</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>43420</v>
+      </c>
+      <c r="B99" t="n">
+        <v>56.45999908447266</v>
+      </c>
+      <c r="C99" t="n">
+        <v>52.91220296926797</v>
+      </c>
+      <c r="D99" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3.54779611520469</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2.739997863769545</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3.54779611520469</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2.739997863769545</v>
+      </c>
+      <c r="I99" t="n">
+        <v>12.58685727506149</v>
+      </c>
+      <c r="J99" t="n">
+        <v>7.507588293461673</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>43427</v>
+      </c>
+      <c r="B100" t="n">
+        <v>50.41999816894531</v>
+      </c>
+      <c r="C100" t="n">
+        <v>50.26256543121101</v>
+      </c>
+      <c r="D100" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.1574327377343039</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-3.300003051757805</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.1574327377343039</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3.300003051757805</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.02478506691051811</v>
+      </c>
+      <c r="J100" t="n">
+        <v>10.89002014161083</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>43434</v>
+      </c>
+      <c r="B101" t="n">
+        <v>50.93000030517578</v>
+      </c>
+      <c r="C101" t="n">
+        <v>51.61682586961219</v>
+      </c>
+      <c r="D101" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-0.6868255644364041</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-2.790000915527337</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.6868255644364041</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2.790000915527337</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.4717293559633851</v>
+      </c>
+      <c r="J101" t="n">
+        <v>7.784105108643376</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>43441</v>
+      </c>
+      <c r="B102" t="n">
+        <v>52.61000061035156</v>
+      </c>
+      <c r="C102" t="n">
+        <v>52.06669900923499</v>
+      </c>
+      <c r="D102" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.5433016011165748</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-1.110000610351555</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.5433016011165748</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1.110000610351555</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.2951766297758337</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1.232101354980826</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>43448</v>
+      </c>
+      <c r="B103" t="n">
+        <v>51.20000076293945</v>
+      </c>
+      <c r="C103" t="n">
+        <v>51.15803422030616</v>
+      </c>
+      <c r="D103" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.04196654263328981</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-2.520000457763665</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.04196654263328981</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2.520000457763665</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.001761190700591731</v>
+      </c>
+      <c r="J103" t="n">
+        <v>6.35040230712908</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>43455</v>
+      </c>
+      <c r="B104" t="n">
+        <v>45.59000015258789</v>
+      </c>
+      <c r="C104" t="n">
+        <v>48.77048223040753</v>
+      </c>
+      <c r="D104" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-3.18048207781964</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-8.130001068115227</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3.18048207781964</v>
+      </c>
+      <c r="H104" t="n">
+        <v>8.130001068115227</v>
+      </c>
+      <c r="I104" t="n">
+        <v>10.11546624733194</v>
+      </c>
+      <c r="J104" t="n">
+        <v>66.09691736755474</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>43462</v>
+      </c>
+      <c r="B105" t="n">
+        <v>45.33000183105469</v>
+      </c>
+      <c r="C105" t="n">
+        <v>48.42502984505814</v>
+      </c>
+      <c r="D105" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-3.095028014003454</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-8.38999938964843</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3.095028014003454</v>
+      </c>
+      <c r="H105" t="n">
+        <v>8.38999938964843</v>
+      </c>
+      <c r="I105" t="n">
+        <v>9.579198407466162</v>
+      </c>
+      <c r="J105" t="n">
+        <v>70.39208975830104</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>43469</v>
+      </c>
+      <c r="B106" t="n">
+        <v>47.95999908447266</v>
+      </c>
+      <c r="C106" t="n">
+        <v>48.16037299319947</v>
+      </c>
+      <c r="D106" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-0.2003739087268102</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-5.760002136230455</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.2003739087268102</v>
+      </c>
+      <c r="H106" t="n">
+        <v>5.760002136230455</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.04014970329846005</v>
+      </c>
+      <c r="J106" t="n">
+        <v>33.1776246093794</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>43476</v>
+      </c>
+      <c r="B107" t="n">
+        <v>51.59000015258789</v>
+      </c>
+      <c r="C107" t="n">
+        <v>50.12000100046053</v>
+      </c>
+      <c r="D107" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1.469999152127365</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-2.130001068115227</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.469999152127365</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2.130001068115227</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2.160897507255171</v>
+      </c>
+      <c r="J107" t="n">
+        <v>4.536904550172009</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>43483</v>
+      </c>
+      <c r="B108" t="n">
+        <v>53.79999923706055</v>
+      </c>
+      <c r="C108" t="n">
+        <v>52.01161115603316</v>
+      </c>
+      <c r="D108" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1.788388081027385</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.07999801635742898</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.788388081027385</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.07999801635742898</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3.198331928360813</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.006399682621123475</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>43490</v>
+      </c>
+      <c r="B109" t="n">
+        <v>53.68999862670898</v>
+      </c>
+      <c r="C109" t="n">
+        <v>51.83348907012208</v>
+      </c>
+      <c r="D109" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1.856509556586893</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-0.03000259399414062</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.856509556586893</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.03000259399414062</v>
+      </c>
+      <c r="I109" t="n">
+        <v>3.446627733698462</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.0009001556463772431</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>43497</v>
+      </c>
+      <c r="B110" t="n">
+        <v>55.2599983215332</v>
+      </c>
+      <c r="C110" t="n">
+        <v>51.86116901623356</v>
+      </c>
+      <c r="D110" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.398829305299643</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.539997100830085</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3.398829305299643</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.539997100830085</v>
+      </c>
+      <c r="I110" t="n">
+        <v>11.55204064656365</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2.371591070565068</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>43504</v>
+      </c>
+      <c r="B111" t="n">
+        <v>52.72000122070312</v>
+      </c>
+      <c r="C111" t="n">
+        <v>50.95944103846597</v>
+      </c>
+      <c r="D111" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1.76056018223715</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.76056018223715</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="n">
+        <v>3.099572155278906</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>43511</v>
+      </c>
+      <c r="B112" t="n">
+        <v>55.59000015258789</v>
+      </c>
+      <c r="C112" t="n">
+        <v>51.23499440715129</v>
+      </c>
+      <c r="D112" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4.3550057454366</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.869998931884773</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4.3550057454366</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1.869998931884773</v>
+      </c>
+      <c r="I112" t="n">
+        <v>18.96607504278579</v>
+      </c>
+      <c r="J112" t="n">
+        <v>3.496896005250191</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>43518</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57.2599983215332</v>
+      </c>
+      <c r="C113" t="n">
+        <v>52.58534031339819</v>
+      </c>
+      <c r="D113" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E113" t="n">
+        <v>4.674658008135012</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3.539997100830085</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4.674658008135012</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3.539997100830085</v>
+      </c>
+      <c r="I113" t="n">
+        <v>21.85242749302079</v>
+      </c>
+      <c r="J113" t="n">
+        <v>12.53157947388541</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>43525</v>
+      </c>
+      <c r="B114" t="n">
+        <v>55.79999923706055</v>
+      </c>
+      <c r="C114" t="n">
+        <v>52.74564192676779</v>
+      </c>
+      <c r="D114" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3.054357310292758</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.079998016357429</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3.054357310292758</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2.079998016357429</v>
+      </c>
+      <c r="I114" t="n">
+        <v>9.329098578938812</v>
+      </c>
+      <c r="J114" t="n">
+        <v>4.326391748050839</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>43532</v>
+      </c>
+      <c r="B115" t="n">
+        <v>56.06999969482422</v>
+      </c>
+      <c r="C115" t="n">
+        <v>51.55580704734359</v>
+      </c>
+      <c r="D115" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4.514192647480627</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2.349998474121101</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4.514192647480627</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2.349998474121101</v>
+      </c>
+      <c r="I115" t="n">
+        <v>20.37793525856815</v>
+      </c>
+      <c r="J115" t="n">
+        <v>5.522492828371503</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>43539</v>
+      </c>
+      <c r="B116" t="n">
+        <v>58.52000045776367</v>
+      </c>
+      <c r="C116" t="n">
+        <v>52.84764873669856</v>
+      </c>
+      <c r="D116" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E116" t="n">
+        <v>5.672351721065112</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4.799999237060554</v>
+      </c>
+      <c r="G116" t="n">
+        <v>5.672351721065112</v>
+      </c>
+      <c r="H116" t="n">
+        <v>4.799999237060554</v>
+      </c>
+      <c r="I116" t="n">
+        <v>32.17557404747034</v>
+      </c>
+      <c r="J116" t="n">
+        <v>23.0399926757819</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>43546</v>
+      </c>
+      <c r="B117" t="n">
+        <v>59.04000091552734</v>
+      </c>
+      <c r="C117" t="n">
+        <v>52.01370145519085</v>
+      </c>
+      <c r="D117" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E117" t="n">
+        <v>7.026299460336482</v>
+      </c>
+      <c r="F117" t="n">
+        <v>5.319999694824219</v>
+      </c>
+      <c r="G117" t="n">
+        <v>7.026299460336482</v>
+      </c>
+      <c r="H117" t="n">
+        <v>5.319999694824219</v>
+      </c>
+      <c r="I117" t="n">
+        <v>49.36888410632474</v>
+      </c>
+      <c r="J117" t="n">
+        <v>28.30239675292978</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>43553</v>
+      </c>
+      <c r="B118" t="n">
+        <v>60.13999938964844</v>
+      </c>
+      <c r="C118" t="n">
+        <v>52.04895708542323</v>
+      </c>
+      <c r="D118" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E118" t="n">
+        <v>8.091042304225212</v>
+      </c>
+      <c r="F118" t="n">
+        <v>6.41999816894532</v>
+      </c>
+      <c r="G118" t="n">
+        <v>8.091042304225212</v>
+      </c>
+      <c r="H118" t="n">
+        <v>6.41999816894532</v>
+      </c>
+      <c r="I118" t="n">
+        <v>65.46496556876203</v>
+      </c>
+      <c r="J118" t="n">
+        <v>41.21637648926126</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>43560</v>
+      </c>
+      <c r="B119" t="n">
+        <v>63.08000183105469</v>
+      </c>
+      <c r="C119" t="n">
+        <v>53.12466947460831</v>
+      </c>
+      <c r="D119" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E119" t="n">
+        <v>9.955332356446377</v>
+      </c>
+      <c r="F119" t="n">
+        <v>9.36000061035157</v>
+      </c>
+      <c r="G119" t="n">
+        <v>9.955332356446377</v>
+      </c>
+      <c r="H119" t="n">
+        <v>9.36000061035157</v>
+      </c>
+      <c r="I119" t="n">
+        <v>99.10864232730816</v>
+      </c>
+      <c r="J119" t="n">
+        <v>87.60961142578175</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>43567</v>
+      </c>
+      <c r="B120" t="n">
+        <v>63.88999938964844</v>
+      </c>
+      <c r="C120" t="n">
+        <v>53.25960367973677</v>
+      </c>
+      <c r="D120" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E120" t="n">
+        <v>10.63039570991167</v>
+      </c>
+      <c r="F120" t="n">
+        <v>10.16999816894532</v>
+      </c>
+      <c r="G120" t="n">
+        <v>10.63039570991167</v>
+      </c>
+      <c r="H120" t="n">
+        <v>10.16999816894532</v>
+      </c>
+      <c r="I120" t="n">
+        <v>113.0053129493084</v>
+      </c>
+      <c r="J120" t="n">
+        <v>103.4288627563512</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>43574</v>
+      </c>
+      <c r="B121" t="n">
+        <v>64</v>
+      </c>
+      <c r="C121" t="n">
+        <v>52.67646452962126</v>
+      </c>
+      <c r="D121" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E121" t="n">
+        <v>11.32353547037874</v>
+      </c>
+      <c r="F121" t="n">
+        <v>10.27999877929688</v>
+      </c>
+      <c r="G121" t="n">
+        <v>11.32353547037874</v>
+      </c>
+      <c r="H121" t="n">
+        <v>10.27999877929688</v>
+      </c>
+      <c r="I121" t="n">
+        <v>128.2224555489254</v>
+      </c>
+      <c r="J121" t="n">
+        <v>105.6783749023454</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>43581</v>
+      </c>
+      <c r="B122" t="n">
+        <v>63.29999923706055</v>
+      </c>
+      <c r="C122" t="n">
+        <v>51.47531843939613</v>
+      </c>
+      <c r="D122" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E122" t="n">
+        <v>11.82468079766441</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9.579998016357429</v>
+      </c>
+      <c r="G122" t="n">
+        <v>11.82468079766441</v>
+      </c>
+      <c r="H122" t="n">
+        <v>9.579998016357429</v>
+      </c>
+      <c r="I122" t="n">
+        <v>139.8230759666535</v>
+      </c>
+      <c r="J122" t="n">
+        <v>91.77636199341228</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>43588</v>
+      </c>
+      <c r="B123" t="n">
+        <v>61.93999862670898</v>
+      </c>
+      <c r="C123" t="n">
+        <v>51.21140355489673</v>
+      </c>
+      <c r="D123" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E123" t="n">
+        <v>10.72859507181225</v>
+      </c>
+      <c r="F123" t="n">
+        <v>8.219997406005859</v>
+      </c>
+      <c r="G123" t="n">
+        <v>10.72859507181225</v>
+      </c>
+      <c r="H123" t="n">
+        <v>8.219997406005859</v>
+      </c>
+      <c r="I123" t="n">
+        <v>115.1027522149141</v>
+      </c>
+      <c r="J123" t="n">
+        <v>67.56835735474306</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>43595</v>
+      </c>
+      <c r="B124" t="n">
+        <v>61.65999984741211</v>
+      </c>
+      <c r="C124" t="n">
+        <v>50.16593511547742</v>
+      </c>
+      <c r="D124" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E124" t="n">
+        <v>11.49406473193469</v>
+      </c>
+      <c r="F124" t="n">
+        <v>7.939998626708991</v>
+      </c>
+      <c r="G124" t="n">
+        <v>11.49406473193469</v>
+      </c>
+      <c r="H124" t="n">
+        <v>7.939998626708991</v>
+      </c>
+      <c r="I124" t="n">
+        <v>132.1135240619049</v>
+      </c>
+      <c r="J124" t="n">
+        <v>63.04357819214067</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>43602</v>
+      </c>
+      <c r="B125" t="n">
+        <v>62.7599983215332</v>
+      </c>
+      <c r="C125" t="n">
+        <v>50.02850292763824</v>
+      </c>
+      <c r="D125" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E125" t="n">
+        <v>12.73149539389496</v>
+      </c>
+      <c r="F125" t="n">
+        <v>9.039997100830085</v>
+      </c>
+      <c r="G125" t="n">
+        <v>12.73149539389496</v>
+      </c>
+      <c r="H125" t="n">
+        <v>9.039997100830085</v>
+      </c>
+      <c r="I125" t="n">
+        <v>162.0909749647686</v>
+      </c>
+      <c r="J125" t="n">
+        <v>81.72154758301635</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>43609</v>
+      </c>
+      <c r="B126" t="n">
+        <v>58.63000106811523</v>
+      </c>
+      <c r="C126" t="n">
+        <v>48.99082499696363</v>
+      </c>
+      <c r="D126" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E126" t="n">
+        <v>9.639176071151596</v>
+      </c>
+      <c r="F126" t="n">
+        <v>4.909999847412109</v>
+      </c>
+      <c r="G126" t="n">
+        <v>9.639176071151596</v>
+      </c>
+      <c r="H126" t="n">
+        <v>4.909999847412109</v>
+      </c>
+      <c r="I126" t="n">
+        <v>92.91371533066152</v>
+      </c>
+      <c r="J126" t="n">
+        <v>24.10809850158694</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>43616</v>
+      </c>
+      <c r="B127" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="C127" t="n">
+        <v>45.835042136546</v>
+      </c>
+      <c r="D127" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E127" t="n">
+        <v>7.664957863453999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.2200012207031179</v>
+      </c>
+      <c r="G127" t="n">
+        <v>7.664957863453999</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.2200012207031179</v>
+      </c>
+      <c r="I127" t="n">
+        <v>58.75157904852529</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.04840053711086199</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>43623</v>
+      </c>
+      <c r="B128" t="n">
+        <v>53.9900016784668</v>
+      </c>
+      <c r="C128" t="n">
+        <v>47.33261650239869</v>
+      </c>
+      <c r="D128" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E128" t="n">
+        <v>6.657385176068104</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.270000457763679</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6.657385176068104</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.270000457763679</v>
+      </c>
+      <c r="I128" t="n">
+        <v>44.32077738253134</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.07290024719259619</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>43630</v>
+      </c>
+      <c r="B129" t="n">
+        <v>52.5099983215332</v>
+      </c>
+      <c r="C129" t="n">
+        <v>47.18519689355522</v>
+      </c>
+      <c r="D129" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E129" t="n">
+        <v>5.324801427977988</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-1.210002899169915</v>
+      </c>
+      <c r="G129" t="n">
+        <v>5.324801427977988</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1.210002899169915</v>
+      </c>
+      <c r="I129" t="n">
+        <v>28.35351024739642</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1.464107015999599</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>43637</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57.43000030517578</v>
+      </c>
+      <c r="C130" t="n">
+        <v>48.02553601918044</v>
+      </c>
+      <c r="D130" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E130" t="n">
+        <v>9.404464285995338</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3.709999084472663</v>
+      </c>
+      <c r="G130" t="n">
+        <v>9.404464285995338</v>
+      </c>
+      <c r="H130" t="n">
+        <v>3.709999084472663</v>
+      </c>
+      <c r="I130" t="n">
+        <v>88.44394850656181</v>
+      </c>
+      <c r="J130" t="n">
+        <v>13.764093206788</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>43644</v>
+      </c>
+      <c r="B131" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="C131" t="n">
+        <v>48.72471047903509</v>
+      </c>
+      <c r="D131" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E131" t="n">
+        <v>9.745290741668029</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G131" t="n">
+        <v>9.745290741668029</v>
+      </c>
+      <c r="H131" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I131" t="n">
+        <v>94.97069163964061</v>
+      </c>
+      <c r="J131" t="n">
+        <v>22.5625</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>43651</v>
+      </c>
+      <c r="B132" t="n">
+        <v>57.5099983215332</v>
+      </c>
+      <c r="C132" t="n">
+        <v>49.48327716432235</v>
+      </c>
+      <c r="D132" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E132" t="n">
+        <v>8.026721157210858</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3.789997100830085</v>
+      </c>
+      <c r="G132" t="n">
+        <v>8.026721157210858</v>
+      </c>
+      <c r="H132" t="n">
+        <v>3.789997100830085</v>
+      </c>
+      <c r="I132" t="n">
+        <v>64.42825253561641</v>
+      </c>
+      <c r="J132" t="n">
+        <v>14.36407802430045</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>43658</v>
+      </c>
+      <c r="B133" t="n">
+        <v>60.20999908447266</v>
+      </c>
+      <c r="C133" t="n">
+        <v>50.55955818788876</v>
+      </c>
+      <c r="D133" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E133" t="n">
+        <v>9.650440896583902</v>
+      </c>
+      <c r="F133" t="n">
+        <v>6.489997863769545</v>
+      </c>
+      <c r="G133" t="n">
+        <v>9.650440896583902</v>
+      </c>
+      <c r="H133" t="n">
+        <v>6.489997863769545</v>
+      </c>
+      <c r="I133" t="n">
+        <v>93.13100949845911</v>
+      </c>
+      <c r="J133" t="n">
+        <v>42.12007227173326</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>43665</v>
+      </c>
+      <c r="B134" t="n">
+        <v>55.63000106811523</v>
+      </c>
+      <c r="C134" t="n">
+        <v>49.5617486694269</v>
+      </c>
+      <c r="D134" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E134" t="n">
+        <v>6.06825239868833</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.909999847412109</v>
+      </c>
+      <c r="G134" t="n">
+        <v>6.06825239868833</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1.909999847412109</v>
+      </c>
+      <c r="I134" t="n">
+        <v>36.82368717418667</v>
+      </c>
+      <c r="J134" t="n">
+        <v>3.648099417114281</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>43672</v>
+      </c>
+      <c r="B135" t="n">
+        <v>56.20000076293945</v>
+      </c>
+      <c r="C135" t="n">
+        <v>49.09947260459465</v>
+      </c>
+      <c r="D135" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E135" t="n">
+        <v>7.100528158344808</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.479999542236335</v>
+      </c>
+      <c r="G135" t="n">
+        <v>7.100528158344808</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2.479999542236335</v>
+      </c>
+      <c r="I135" t="n">
+        <v>50.41750012744751</v>
+      </c>
+      <c r="J135" t="n">
+        <v>6.150397729492433</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>43679</v>
+      </c>
+      <c r="B136" t="n">
+        <v>55.65999984741211</v>
+      </c>
+      <c r="C136" t="n">
+        <v>47.75291818542205</v>
+      </c>
+      <c r="D136" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E136" t="n">
+        <v>7.907081661990063</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.939998626708991</v>
+      </c>
+      <c r="G136" t="n">
+        <v>7.907081661990063</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1.939998626708991</v>
+      </c>
+      <c r="I136" t="n">
+        <v>62.52194040937953</v>
+      </c>
+      <c r="J136" t="n">
+        <v>3.763594671632773</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>43686</v>
+      </c>
+      <c r="B137" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="C137" t="n">
+        <v>48.2411705483514</v>
+      </c>
+      <c r="D137" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E137" t="n">
+        <v>6.258829451648602</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.7799987792968821</v>
+      </c>
+      <c r="G137" t="n">
+        <v>6.258829451648602</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7799987792968821</v>
+      </c>
+      <c r="I137" t="n">
+        <v>39.17294610482394</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.6083980957046262</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>43693</v>
+      </c>
+      <c r="B138" t="n">
+        <v>54.86999893188477</v>
+      </c>
+      <c r="C138" t="n">
+        <v>47.77703987883032</v>
+      </c>
+      <c r="D138" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E138" t="n">
+        <v>7.09295905305445</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.149997711181655</v>
+      </c>
+      <c r="G138" t="n">
+        <v>7.09295905305445</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1.149997711181655</v>
+      </c>
+      <c r="I138" t="n">
+        <v>50.31006812830708</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1.322494735723045</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>43700</v>
+      </c>
+      <c r="B139" t="n">
+        <v>54.16999816894531</v>
+      </c>
+      <c r="C139" t="n">
+        <v>47.11741166729806</v>
+      </c>
+      <c r="D139" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E139" t="n">
+        <v>7.052586501647255</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.4499969482421946</v>
+      </c>
+      <c r="G139" t="n">
+        <v>7.052586501647255</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.4499969482421946</v>
+      </c>
+      <c r="I139" t="n">
+        <v>49.73897636321707</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.2024972534272884</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>43707</v>
+      </c>
+      <c r="B140" t="n">
+        <v>55.09999847412109</v>
+      </c>
+      <c r="C140" t="n">
+        <v>47.69057274388442</v>
+      </c>
+      <c r="D140" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E140" t="n">
+        <v>7.40942573023667</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.379997253417969</v>
+      </c>
+      <c r="G140" t="n">
+        <v>7.40942573023667</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1.379997253417969</v>
+      </c>
+      <c r="I140" t="n">
+        <v>54.89958965189321</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.904392419441137</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>43714</v>
+      </c>
+      <c r="B141" t="n">
+        <v>56.52000045776367</v>
+      </c>
+      <c r="C141" t="n">
+        <v>48.73538534138309</v>
+      </c>
+      <c r="D141" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E141" t="n">
+        <v>7.784615116380586</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2.799999237060554</v>
+      </c>
+      <c r="G141" t="n">
+        <v>7.784615116380586</v>
+      </c>
+      <c r="H141" t="n">
+        <v>2.799999237060554</v>
+      </c>
+      <c r="I141" t="n">
+        <v>60.60023251018112</v>
+      </c>
+      <c r="J141" t="n">
+        <v>7.839995727539685</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>43721</v>
+      </c>
+      <c r="B142" t="n">
+        <v>54.84999847412109</v>
+      </c>
+      <c r="C142" t="n">
+        <v>49.78318124347706</v>
+      </c>
+      <c r="D142" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E142" t="n">
+        <v>5.066817230644027</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.129997253417969</v>
+      </c>
+      <c r="G142" t="n">
+        <v>5.066817230644027</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1.129997253417969</v>
+      </c>
+      <c r="I142" t="n">
+        <v>25.67263684875121</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1.276893792732153</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>43728</v>
+      </c>
+      <c r="B143" t="n">
+        <v>58.09000015258789</v>
+      </c>
+      <c r="C143" t="n">
+        <v>48.06216215683801</v>
+      </c>
+      <c r="D143" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E143" t="n">
+        <v>10.02783799574988</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4.369998931884773</v>
+      </c>
+      <c r="G143" t="n">
+        <v>10.02783799574988</v>
+      </c>
+      <c r="H143" t="n">
+        <v>4.369998931884773</v>
+      </c>
+      <c r="I143" t="n">
+        <v>100.5575348690051</v>
+      </c>
+      <c r="J143" t="n">
+        <v>19.09689066467405</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>43735</v>
+      </c>
+      <c r="B144" t="n">
+        <v>55.90999984741211</v>
+      </c>
+      <c r="C144" t="n">
+        <v>47.64085664183656</v>
+      </c>
+      <c r="D144" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E144" t="n">
+        <v>8.269143205575553</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2.189998626708991</v>
+      </c>
+      <c r="G144" t="n">
+        <v>8.269143205575553</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2.189998626708991</v>
+      </c>
+      <c r="I144" t="n">
+        <v>68.37872935431633</v>
+      </c>
+      <c r="J144" t="n">
+        <v>4.796093984987269</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>43742</v>
+      </c>
+      <c r="B145" t="n">
+        <v>52.81000137329102</v>
+      </c>
+      <c r="C145" t="n">
+        <v>46.78377361334687</v>
+      </c>
+      <c r="D145" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E145" t="n">
+        <v>6.026227759944149</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-0.9099998474120952</v>
+      </c>
+      <c r="G145" t="n">
+        <v>6.026227759944149</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.9099998474120952</v>
+      </c>
+      <c r="I145" t="n">
+        <v>36.31542101472147</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.8280997222900365</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>43749</v>
+      </c>
+      <c r="B146" t="n">
+        <v>54.70000076293945</v>
+      </c>
+      <c r="C146" t="n">
+        <v>47.17614482908007</v>
+      </c>
+      <c r="D146" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E146" t="n">
+        <v>7.52385593385938</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.9799995422363352</v>
+      </c>
+      <c r="G146" t="n">
+        <v>7.52385593385938</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.9799995422363352</v>
+      </c>
+      <c r="I146" t="n">
+        <v>56.60840811347101</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.9603991027834266</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>43756</v>
+      </c>
+      <c r="B147" t="n">
+        <v>53.77999877929688</v>
+      </c>
+      <c r="C147" t="n">
+        <v>48.2957303987229</v>
+      </c>
+      <c r="D147" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E147" t="n">
+        <v>5.48426838057398</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.05999755859376421</v>
+      </c>
+      <c r="G147" t="n">
+        <v>5.48426838057398</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.05999755859376421</v>
+      </c>
+      <c r="I147" t="n">
+        <v>30.07719967016354</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.00359970703721217</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>43763</v>
+      </c>
+      <c r="B148" t="n">
+        <v>56.65999984741211</v>
+      </c>
+      <c r="C148" t="n">
+        <v>48.77732508093231</v>
+      </c>
+      <c r="D148" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E148" t="n">
+        <v>7.882674766479795</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2.939998626708991</v>
+      </c>
+      <c r="G148" t="n">
+        <v>7.882674766479795</v>
+      </c>
+      <c r="H148" t="n">
+        <v>2.939998626708991</v>
+      </c>
+      <c r="I148" t="n">
+        <v>62.13656147409729</v>
+      </c>
+      <c r="J148" t="n">
+        <v>8.643591925050757</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>43770</v>
+      </c>
+      <c r="B149" t="n">
+        <v>56.20000076293945</v>
+      </c>
+      <c r="C149" t="n">
+        <v>49.73752421364728</v>
+      </c>
+      <c r="D149" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E149" t="n">
+        <v>6.46247654929217</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.479999542236335</v>
+      </c>
+      <c r="G149" t="n">
+        <v>6.46247654929217</v>
+      </c>
+      <c r="H149" t="n">
+        <v>2.479999542236335</v>
+      </c>
+      <c r="I149" t="n">
+        <v>41.76360315015123</v>
+      </c>
+      <c r="J149" t="n">
+        <v>6.150397729492433</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>43777</v>
+      </c>
+      <c r="B150" t="n">
+        <v>57.2400016784668</v>
+      </c>
+      <c r="C150" t="n">
+        <v>50.39502483733148</v>
+      </c>
+      <c r="D150" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E150" t="n">
+        <v>6.84497684113532</v>
+      </c>
+      <c r="F150" t="n">
+        <v>3.520000457763679</v>
+      </c>
+      <c r="G150" t="n">
+        <v>6.84497684113532</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3.520000457763679</v>
+      </c>
+      <c r="I150" t="n">
+        <v>46.85370795567887</v>
+      </c>
+      <c r="J150" t="n">
+        <v>12.39040322265651</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>43784</v>
+      </c>
+      <c r="B151" t="n">
+        <v>57.72000122070312</v>
+      </c>
+      <c r="C151" t="n">
+        <v>49.83907430949299</v>
+      </c>
+      <c r="D151" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E151" t="n">
+        <v>7.880926911210132</v>
+      </c>
+      <c r="F151" t="n">
+        <v>4</v>
+      </c>
+      <c r="G151" t="n">
+        <v>7.880926911210132</v>
+      </c>
+      <c r="H151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I151" t="n">
+        <v>62.10900897983607</v>
+      </c>
+      <c r="J151" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>43791</v>
+      </c>
+      <c r="B152" t="n">
+        <v>57.77000045776367</v>
+      </c>
+      <c r="C152" t="n">
+        <v>49.50007199593671</v>
+      </c>
+      <c r="D152" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E152" t="n">
+        <v>8.269928461826957</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4.049999237060554</v>
+      </c>
+      <c r="G152" t="n">
+        <v>8.269928461826957</v>
+      </c>
+      <c r="H152" t="n">
+        <v>4.049999237060554</v>
+      </c>
+      <c r="I152" t="n">
+        <v>68.39171676373559</v>
+      </c>
+      <c r="J152" t="n">
+        <v>16.40249382019107</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>43798</v>
+      </c>
+      <c r="B153" t="n">
+        <v>55.16999816894531</v>
+      </c>
+      <c r="C153" t="n">
+        <v>47.96660771379326</v>
+      </c>
+      <c r="D153" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E153" t="n">
+        <v>7.203390455152054</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1.449996948242195</v>
+      </c>
+      <c r="G153" t="n">
+        <v>7.203390455152054</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1.449996948242195</v>
+      </c>
+      <c r="I153" t="n">
+        <v>51.88883404937571</v>
+      </c>
+      <c r="J153" t="n">
+        <v>2.102491149911677</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>43805</v>
+      </c>
+      <c r="B154" t="n">
+        <v>59.20000076293945</v>
+      </c>
+      <c r="C154" t="n">
+        <v>49.65005019918842</v>
+      </c>
+      <c r="D154" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E154" t="n">
+        <v>9.549950563751032</v>
+      </c>
+      <c r="F154" t="n">
+        <v>5.479999542236335</v>
+      </c>
+      <c r="G154" t="n">
+        <v>9.549950563751032</v>
+      </c>
+      <c r="H154" t="n">
+        <v>5.479999542236335</v>
+      </c>
+      <c r="I154" t="n">
+        <v>91.20155577008866</v>
+      </c>
+      <c r="J154" t="n">
+        <v>30.03039498291044</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>43812</v>
+      </c>
+      <c r="B155" t="n">
+        <v>60.06999969482422</v>
+      </c>
+      <c r="C155" t="n">
+        <v>50.94699335744819</v>
+      </c>
+      <c r="D155" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E155" t="n">
+        <v>9.123006337376033</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6.349998474121101</v>
+      </c>
+      <c r="G155" t="n">
+        <v>9.123006337376033</v>
+      </c>
+      <c r="H155" t="n">
+        <v>6.349998474121101</v>
+      </c>
+      <c r="I155" t="n">
+        <v>83.22924463180325</v>
+      </c>
+      <c r="J155" t="n">
+        <v>40.32248062134031</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>43819</v>
+      </c>
+      <c r="B156" t="n">
+        <v>60.43999862670898</v>
+      </c>
+      <c r="C156" t="n">
+        <v>51.35371933336278</v>
+      </c>
+      <c r="D156" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E156" t="n">
+        <v>9.086279293346202</v>
+      </c>
+      <c r="F156" t="n">
+        <v>6.719997406005859</v>
+      </c>
+      <c r="G156" t="n">
+        <v>9.086279293346202</v>
+      </c>
+      <c r="H156" t="n">
+        <v>6.719997406005859</v>
+      </c>
+      <c r="I156" t="n">
+        <v>82.56047139669195</v>
+      </c>
+      <c r="J156" t="n">
+        <v>45.15836513672548</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>43826</v>
+      </c>
+      <c r="B157" t="n">
+        <v>61.72000122070312</v>
+      </c>
+      <c r="C157" t="n">
+        <v>51.20746245512095</v>
+      </c>
+      <c r="D157" t="n">
+        <v>53.72000122070312</v>
+      </c>
+      <c r="E157" t="n">
+        <v>10.51253876558217</v>
+      </c>
+      <c r="F157" t="n">
+        <v>8</v>
+      </c>
+      <c r="G157" t="n">
+        <v>10.51253876558217</v>
+      </c>
+      <c r="H157" t="n">
+        <v>8</v>
+      </c>
+      <c r="I157" t="n">
+        <v>110.5134712978679</v>
+      </c>
+      <c r="J157" t="n">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MZ intercept</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>20.4118670796321</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MZ intercept p-value</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.02368503660049203</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MZ slope</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6937936144012682</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MZ slope p-value</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4.959622950372503e-05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MZ R-squared</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1016991648668413</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>